--- a/src/Book2.xlsx
+++ b/src/Book2.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mick/Documents/ApexGirl/CEO Calculators/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88E94718-E541-DF41-8344-69A68DFA49C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F3A7B8-62C1-8649-A6B9-CE4CD095CB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4700" yWindow="3200" windowWidth="27240" windowHeight="16440" xr2:uid="{D8ED658E-D9C5-E147-BCF7-90ED8C2B9DC3}"/>
+    <workbookView xWindow="39480" yWindow="2640" windowWidth="32000" windowHeight="16440" xr2:uid="{D8ED658E-D9C5-E147-BCF7-90ED8C2B9DC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="75">
   <si>
     <t>Calculation points for events</t>
   </si>
@@ -225,6 +225,42 @@
   </si>
   <si>
     <t>APPROXIMATE TOTAL FOR ALL DAYS</t>
+  </si>
+  <si>
+    <t>WARM UP EVENT</t>
+  </si>
+  <si>
+    <t>Innovation</t>
+  </si>
+  <si>
+    <t>Earn 1 Gold Bar in the Hotel</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Use CEO's Coins (Basic)</t>
+  </si>
+  <si>
+    <t>Use CEO's Coins (High-Quality)</t>
+  </si>
+  <si>
+    <t>Use CEO's Coins (Premium)</t>
+  </si>
+  <si>
+    <t>Interview Artist</t>
+  </si>
+  <si>
+    <t>Use Asset Coin</t>
+  </si>
+  <si>
+    <t>Use SR Private Photos</t>
+  </si>
+  <si>
+    <t>Use SSR Private Photos</t>
+  </si>
+  <si>
+    <t>Promotion</t>
   </si>
 </sst>
 </file>
@@ -364,17 +400,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -393,9 +420,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -420,20 +444,32 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -769,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF653535-84BE-3F4E-945D-EA02798F356F}">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" customWidth="1"/>
@@ -779,2356 +815,3225 @@
     <col min="8" max="8" width="23.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.83203125" customWidth="1"/>
+    <col min="14" max="14" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="8" t="s">
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="H3" s="8" t="s">
+      <c r="F3" s="6"/>
+      <c r="H3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="L3" s="6"/>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="10">
         <v>500</v>
       </c>
-      <c r="D4" s="13">
-        <v>10</v>
-      </c>
-      <c r="E4" s="14">
+      <c r="D4" s="10">
+        <v>10</v>
+      </c>
+      <c r="E4" s="11">
         <f>D4*C4</f>
         <v>5000</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="11" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="10">
         <v>500</v>
       </c>
-      <c r="J4" s="13">
-        <v>10</v>
-      </c>
-      <c r="K4" s="14">
+      <c r="J4" s="10">
+        <v>10</v>
+      </c>
+      <c r="K4" s="11">
         <f>J4*I4</f>
         <v>5000</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
+      <c r="L4" s="10"/>
+      <c r="M4" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="10">
+        <v>500</v>
+      </c>
+      <c r="P4" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="11">
+        <f>P4*O4</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="26"/>
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="10">
         <v>2500</v>
       </c>
-      <c r="D5" s="13">
-        <v>10</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="D5" s="10">
+        <v>10</v>
+      </c>
+      <c r="E5" s="11">
         <f t="shared" ref="E5:E16" si="0">D5*C5</f>
         <v>25000</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="12" t="s">
+      <c r="F5" s="10"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="10">
         <v>2500</v>
       </c>
-      <c r="J5" s="13">
-        <v>10</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" ref="K5:K16" si="1">J5*I5</f>
+      <c r="J5" s="10">
+        <v>10</v>
+      </c>
+      <c r="K5" s="11">
+        <f t="shared" ref="K5:K13" si="1">J5*I5</f>
         <v>25000</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="13">
+      <c r="L5" s="10"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="10">
+        <v>2500</v>
+      </c>
+      <c r="P5" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="11">
+        <f t="shared" ref="Q5:Q13" si="2">P5*O5</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="26"/>
+      <c r="B6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10">
         <v>1000</v>
       </c>
-      <c r="D6" s="13">
-        <v>10</v>
-      </c>
-      <c r="E6" s="14">
+      <c r="D6" s="10">
+        <v>10</v>
+      </c>
+      <c r="E6" s="11">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="13">
+      <c r="F6" s="10"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="10">
         <v>1000</v>
       </c>
-      <c r="J6" s="13">
-        <v>10</v>
-      </c>
-      <c r="K6" s="14">
+      <c r="J6" s="10">
+        <v>10</v>
+      </c>
+      <c r="K6" s="11">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
+      <c r="L6" s="10"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="O6" s="10">
+        <v>400</v>
+      </c>
+      <c r="P6" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="11">
+        <f t="shared" si="2"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="26"/>
+      <c r="B7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="10">
         <v>10000</v>
       </c>
-      <c r="D7" s="13">
-        <v>10</v>
-      </c>
-      <c r="E7" s="14">
+      <c r="D7" s="10">
+        <v>10</v>
+      </c>
+      <c r="E7" s="11">
         <f t="shared" si="0"/>
         <v>100000</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12" t="s">
+      <c r="F7" s="10"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="10">
         <v>10000</v>
       </c>
-      <c r="J7" s="13">
-        <v>10</v>
-      </c>
-      <c r="K7" s="14">
+      <c r="J7" s="10">
+        <v>10</v>
+      </c>
+      <c r="K7" s="11">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12" t="s">
+      <c r="L7" s="10"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13">
+      <c r="O7" s="10">
+        <v>50000</v>
+      </c>
+      <c r="P7" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="11">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="26"/>
+      <c r="B8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="10">
         <v>125000</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>152</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="11">
         <f t="shared" si="0"/>
         <v>19000000</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12" t="s">
+      <c r="F8" s="10"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="10">
         <v>125000</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="5">
         <v>152</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="11">
         <f t="shared" si="1"/>
         <v>19000000</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
+      <c r="L8" s="10"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="O8" s="10">
+        <v>125000</v>
+      </c>
+      <c r="P8" s="5">
+        <v>152</v>
+      </c>
+      <c r="Q8" s="11">
+        <f t="shared" si="2"/>
+        <v>19000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="26"/>
+      <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="10">
         <v>1250000</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>9</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="11">
         <f t="shared" si="0"/>
         <v>11250000</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="12" t="s">
+      <c r="F9" s="10"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="10">
         <v>1250000</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="5">
         <v>9</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="11">
         <f t="shared" si="1"/>
         <v>11250000</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12" t="s">
+      <c r="L9" s="10"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="O9" s="10">
+        <v>4000</v>
+      </c>
+      <c r="P9" s="5">
+        <v>9</v>
+      </c>
+      <c r="Q9" s="11">
+        <f t="shared" si="2"/>
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="26"/>
+      <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="10">
         <v>15625000</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="14">
+      <c r="D10" s="5"/>
+      <c r="E10" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="12" t="s">
+      <c r="F10" s="10"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="10">
         <v>15625000</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="14">
+      <c r="J10" s="5"/>
+      <c r="K10" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12" t="s">
+      <c r="L10" s="10"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O10" s="10">
+        <v>500000</v>
+      </c>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="26"/>
+      <c r="B11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="10">
         <v>156250000</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="14">
+      <c r="D11" s="5"/>
+      <c r="E11" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="12" t="s">
+      <c r="F11" s="10"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="10">
         <v>156250000</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="14">
+      <c r="J11" s="5"/>
+      <c r="K11" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12" t="s">
+      <c r="L11" s="10"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" s="10">
+        <v>62500000</v>
+      </c>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="26"/>
+      <c r="B12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="10">
         <v>1</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="14">
+      <c r="D12" s="5"/>
+      <c r="E12" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="12" t="s">
+      <c r="F12" s="10"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="10">
         <v>1</v>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="14">
+      <c r="J12" s="5"/>
+      <c r="K12" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12" t="s">
+      <c r="L12" s="10"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="10">
+        <v>500</v>
+      </c>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="26"/>
+      <c r="B13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="10">
         <v>50000</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="14">
+      <c r="D13" s="5"/>
+      <c r="E13" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="12" t="s">
+      <c r="F13" s="10"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="10">
         <v>50000</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="14">
+      <c r="J13" s="5"/>
+      <c r="K13" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="L13" s="10"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="10">
+        <v>400</v>
+      </c>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="26"/>
+      <c r="B14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="10">
         <v>1</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>1000000</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="11">
         <f>(D14*C14)/24</f>
         <v>41666.666666666664</v>
       </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="12" t="s">
+      <c r="F14" s="10"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="10">
         <v>1</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="5">
         <v>1000000</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="11">
         <f>(J14*I14)/24</f>
         <v>41666.666666666664</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12" t="s">
+      <c r="L14" s="10"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="10">
+        <v>50000</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="Q14" s="11">
+        <f>P14*O14</f>
+        <v>50000000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="26"/>
+      <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="10">
         <v>10000</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12" t="s">
+      <c r="F15" s="10"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="10">
         <v>10000</v>
       </c>
-      <c r="K15" s="14">
-        <f t="shared" ref="K15:K26" si="2">J15*I15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12" t="s">
+      <c r="K15" s="11">
+        <f t="shared" ref="K15:K16" si="3">J15*I15</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="10"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O15" s="10">
+        <v>6250000</v>
+      </c>
+      <c r="Q15" s="11">
+        <f t="shared" ref="Q15:Q24" si="4">P15*O15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="26"/>
+      <c r="B16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="10">
         <v>40000</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12" t="s">
+      <c r="F16" s="10"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="10">
         <v>40000</v>
       </c>
-      <c r="K16" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16" t="s">
+      <c r="K16" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" s="10">
+        <v>4000</v>
+      </c>
+      <c r="Q16" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12"/>
+      <c r="B17" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18">
+      <c r="C17" s="23"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14">
         <f>SUM(E4:E16)</f>
         <v>30431666.666666668</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16" t="s">
+      <c r="F17" s="15"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="18">
+      <c r="I17" s="23"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="14">
         <f>SUM(K4:K16)</f>
         <v>30431666.666666668</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="L17" s="15"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="10">
+        <v>500000</v>
+      </c>
+      <c r="Q17" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="10">
         <v>500</v>
       </c>
-      <c r="D18" s="13">
-        <v>10</v>
-      </c>
-      <c r="E18" s="20">
+      <c r="D18" s="10">
+        <v>10</v>
+      </c>
+      <c r="E18" s="16">
         <f>D18*C18</f>
         <v>5000</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="11" t="s">
+      <c r="F18" s="5"/>
+      <c r="G18" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="10">
         <v>500</v>
       </c>
-      <c r="J18" s="13">
-        <v>10</v>
-      </c>
-      <c r="K18" s="20">
+      <c r="J18" s="10">
+        <v>10</v>
+      </c>
+      <c r="K18" s="16">
         <f>J18*I18</f>
         <v>5000</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12" t="s">
+      <c r="L18" s="5"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="10">
+        <v>62500000</v>
+      </c>
+      <c r="Q18" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="26"/>
+      <c r="B19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="10">
         <v>1000</v>
       </c>
-      <c r="D19" s="13">
-        <v>10</v>
-      </c>
-      <c r="E19" s="20">
-        <f t="shared" ref="E19:E29" si="3">D19*C19</f>
+      <c r="D19" s="10">
+        <v>10</v>
+      </c>
+      <c r="E19" s="16">
+        <f t="shared" ref="E19:E29" si="5">D19*C19</f>
         <v>10000</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="12" t="s">
+      <c r="F19" s="5"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="10">
         <v>1000</v>
       </c>
-      <c r="J19" s="13">
-        <v>10</v>
-      </c>
-      <c r="K19" s="20">
-        <f t="shared" ref="K19:K29" si="4">J19*I19</f>
+      <c r="J19" s="10">
+        <v>10</v>
+      </c>
+      <c r="K19" s="16">
+        <f t="shared" ref="K19:K26" si="6">J19*I19</f>
         <v>10000</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12" t="s">
+      <c r="L19" s="5"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O19" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A20" s="26"/>
+      <c r="B20" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="10">
         <v>10000</v>
       </c>
-      <c r="D20" s="13">
-        <v>10</v>
-      </c>
-      <c r="E20" s="20">
-        <f t="shared" si="3"/>
+      <c r="D20" s="10">
+        <v>10</v>
+      </c>
+      <c r="E20" s="16">
+        <f t="shared" si="5"/>
         <v>100000</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="12" t="s">
+      <c r="F20" s="5"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="10">
         <v>10000</v>
       </c>
-      <c r="J20" s="13">
-        <v>10</v>
-      </c>
-      <c r="K20" s="20">
+      <c r="J20" s="10">
+        <v>10</v>
+      </c>
+      <c r="K20" s="16">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="L20" s="5"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O20" s="10">
+        <v>50000</v>
+      </c>
+      <c r="Q20" s="11">
         <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A21" s="26"/>
+      <c r="B21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="10">
         <v>125000</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="12" t="s">
+      <c r="D21" s="10"/>
+      <c r="E21" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="10">
         <v>125000</v>
       </c>
-      <c r="J21" s="13"/>
-      <c r="K21" s="20">
+      <c r="J21" s="10"/>
+      <c r="K21" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="11">
+        <f>(P21*O21)/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22" s="26"/>
+      <c r="B22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="10">
+        <v>1250000</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="10">
+        <v>1250000</v>
+      </c>
+      <c r="J22" s="10"/>
+      <c r="K22" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O22" s="10">
+        <v>10000</v>
+      </c>
+      <c r="Q22" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="13">
-        <v>1250000</v>
-      </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" s="13">
-        <v>1250000</v>
-      </c>
-      <c r="J22" s="13"/>
-      <c r="K22" s="20">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" s="26"/>
+      <c r="B23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="10">
+        <v>15625000</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="10">
+        <v>15625000</v>
+      </c>
+      <c r="J23" s="5"/>
+      <c r="K23" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" s="10">
+        <v>40000</v>
+      </c>
+      <c r="Q23" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="13">
-        <v>15625000</v>
-      </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="13">
-        <v>15625000</v>
-      </c>
-      <c r="J23" s="7"/>
-      <c r="K23" s="20">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A24" s="26"/>
+      <c r="B24" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="10">
+        <v>156250000</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="10">
+        <v>156250000</v>
+      </c>
+      <c r="J24" s="5"/>
+      <c r="K24" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="13">
-        <v>156250000</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I24" s="13">
-        <v>156250000</v>
-      </c>
-      <c r="J24" s="7"/>
-      <c r="K24" s="20">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12" t="s">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A25" s="26"/>
+      <c r="B25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="10">
         <v>1</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="12" t="s">
+      <c r="D25" s="5"/>
+      <c r="E25" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="10">
         <v>1</v>
       </c>
-      <c r="J25" s="7"/>
-      <c r="K25" s="20">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12" t="s">
+      <c r="J25" s="5"/>
+      <c r="K25" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="N25" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" s="23"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="14">
+        <f>SUM(Q4:Q24)</f>
+        <v>50019570000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A26" s="26"/>
+      <c r="B26" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="10">
         <v>50000</v>
       </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="12" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="10">
         <v>50000</v>
       </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="20">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12" t="s">
+      <c r="J26" s="5"/>
+      <c r="K26" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O26" s="20">
+        <v>500</v>
+      </c>
+      <c r="P26" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="16">
+        <f>O26*P26</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A27" s="26"/>
+      <c r="B27" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="10">
         <v>1</v>
       </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="20">
+      <c r="D27" s="5"/>
+      <c r="E27" s="16">
         <f>D27*C27/24</f>
         <v>0</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12" t="s">
+      <c r="F27" s="5"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="10">
         <v>1</v>
       </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="20">
+      <c r="J27" s="5"/>
+      <c r="K27" s="16">
         <f>J27*I27/24</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12" t="s">
+      <c r="L27" s="5"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O27" s="20">
+        <v>1000</v>
+      </c>
+      <c r="P27" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="16">
+        <f t="shared" ref="Q27:Q47" si="7">O27*P27</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A28" s="26"/>
+      <c r="B28" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="10">
         <v>10000</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="12" t="s">
+      <c r="D28" s="5"/>
+      <c r="E28" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="10">
         <v>10000</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="20">
-        <f t="shared" ref="K28:K38" si="5">J28*I28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="16">
+        <f t="shared" ref="K28:K29" si="8">J28*I28</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O28" s="9">
+        <v>1000</v>
+      </c>
+      <c r="P28" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q28" s="16">
+        <f t="shared" si="7"/>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A29" s="26"/>
+      <c r="B29" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="10">
         <v>40000</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="12" t="s">
+      <c r="D29" s="5"/>
+      <c r="E29" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="10">
         <v>40000</v>
       </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="20">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
-      <c r="B30" s="16" t="s">
+      <c r="J29" s="5"/>
+      <c r="K29" s="16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O29" s="9">
+        <v>125000</v>
+      </c>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="17"/>
+      <c r="B30" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="22">
+      <c r="C30" s="23"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="18">
         <f>SUM(E18:E29)</f>
         <v>115000</v>
       </c>
-      <c r="F30" s="23"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="16" t="s">
+      <c r="F30" s="19"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="16"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="22">
+      <c r="I30" s="23"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="18">
         <f>SUM(K18:K29)</f>
         <v>115000</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
+      <c r="L30" s="19"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" s="9">
+        <v>15625000</v>
+      </c>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="20">
         <v>500</v>
       </c>
-      <c r="D31" s="13">
-        <v>10</v>
-      </c>
-      <c r="E31" s="20">
+      <c r="D31" s="10">
+        <v>10</v>
+      </c>
+      <c r="E31" s="16">
         <f>C31*D31</f>
         <v>5000</v>
       </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="11" t="s">
+      <c r="F31" s="5"/>
+      <c r="G31" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="20">
         <v>500</v>
       </c>
-      <c r="J31" s="13">
-        <v>10</v>
-      </c>
-      <c r="K31" s="20">
+      <c r="J31" s="10">
+        <v>10</v>
+      </c>
+      <c r="K31" s="16">
         <f>I31*J31</f>
         <v>5000</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12" t="s">
+      <c r="L31" s="5"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="O31" s="9">
+        <v>10000</v>
+      </c>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="26"/>
+      <c r="B32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="20">
         <v>1000</v>
       </c>
-      <c r="D32" s="13">
-        <v>10</v>
-      </c>
-      <c r="E32" s="20">
-        <f t="shared" ref="E32:E43" si="6">C32*D32</f>
+      <c r="D32" s="10">
+        <v>10</v>
+      </c>
+      <c r="E32" s="16">
+        <f t="shared" ref="E32:E43" si="9">C32*D32</f>
         <v>10000</v>
       </c>
-      <c r="F32" s="7"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="12" t="s">
+      <c r="F32" s="5"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="20">
         <v>1000</v>
       </c>
-      <c r="J32" s="13">
-        <v>10</v>
-      </c>
-      <c r="K32" s="20">
-        <f t="shared" ref="K32:K43" si="7">I32*J32</f>
+      <c r="J32" s="10">
+        <v>10</v>
+      </c>
+      <c r="K32" s="16">
+        <f t="shared" ref="K32:K40" si="10">I32*J32</f>
         <v>10000</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12" t="s">
+      <c r="L32" s="5"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O32" s="9">
+        <v>1250000</v>
+      </c>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A33" s="26"/>
+      <c r="B33" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="9">
         <v>2000</v>
       </c>
-      <c r="D33" s="13">
-        <v>10</v>
-      </c>
-      <c r="E33" s="20">
-        <f t="shared" si="6"/>
+      <c r="D33" s="10">
+        <v>10</v>
+      </c>
+      <c r="E33" s="16">
+        <f t="shared" si="9"/>
         <v>20000</v>
       </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12" t="s">
+      <c r="F33" s="5"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="9">
         <v>2000</v>
       </c>
-      <c r="J33" s="13">
-        <v>10</v>
-      </c>
-      <c r="K33" s="20">
+      <c r="J33" s="10">
+        <v>10</v>
+      </c>
+      <c r="K33" s="16">
+        <f t="shared" si="10"/>
+        <v>20000</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33" s="9">
+        <v>156250000</v>
+      </c>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="16">
         <f t="shared" si="7"/>
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A34" s="26"/>
+      <c r="B34" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C34">
         <v>20000</v>
       </c>
-      <c r="D34" s="13">
-        <v>10</v>
-      </c>
-      <c r="E34" s="20">
-        <f t="shared" si="6"/>
+      <c r="D34" s="10">
+        <v>10</v>
+      </c>
+      <c r="E34" s="16">
+        <f t="shared" si="9"/>
         <v>200000</v>
       </c>
-      <c r="F34" s="7"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12" t="s">
+      <c r="F34" s="5"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="9" t="s">
         <v>34</v>
       </c>
       <c r="I34">
         <v>20000</v>
       </c>
-      <c r="J34" s="13">
-        <v>10</v>
-      </c>
-      <c r="K34" s="20">
+      <c r="J34" s="10">
+        <v>10</v>
+      </c>
+      <c r="K34" s="16">
+        <f t="shared" si="10"/>
+        <v>200000</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="O34" s="9">
+        <v>500</v>
+      </c>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="16">
         <f t="shared" si="7"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A35" s="26"/>
+      <c r="B35" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C35">
         <v>250000</v>
       </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12" t="s">
+      <c r="D35" s="5"/>
+      <c r="E35" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I35">
         <v>250000</v>
       </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="20">
+      <c r="J35" s="5"/>
+      <c r="K35" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O35" s="9">
+        <v>5000</v>
+      </c>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12" t="s">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36" s="26"/>
+      <c r="B36" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C36">
         <v>2500000</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12" t="s">
+      <c r="D36" s="5"/>
+      <c r="E36" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="9" t="s">
         <v>36</v>
       </c>
       <c r="I36">
         <v>2500000</v>
       </c>
-      <c r="J36" s="7"/>
-      <c r="K36" s="20">
+      <c r="J36" s="5"/>
+      <c r="K36" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O36" s="9">
+        <v>1000</v>
+      </c>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
-      <c r="B37" s="12" t="s">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A37" s="26"/>
+      <c r="B37" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C37">
         <v>31250000</v>
       </c>
-      <c r="D37" s="7"/>
-      <c r="E37" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="7"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12" t="s">
+      <c r="D37" s="5"/>
+      <c r="E37" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="9" t="s">
         <v>37</v>
       </c>
       <c r="I37">
         <v>31250000</v>
       </c>
-      <c r="J37" s="7"/>
-      <c r="K37" s="20">
+      <c r="J37" s="5"/>
+      <c r="K37" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O37" s="9">
+        <v>125000</v>
+      </c>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12" t="s">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A38" s="26"/>
+      <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
       <c r="C38">
         <v>312500000</v>
       </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12" t="s">
+      <c r="D38" s="5"/>
+      <c r="E38" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="5"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="9" t="s">
         <v>38</v>
       </c>
       <c r="I38">
         <v>312500000</v>
       </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="20">
+      <c r="J38" s="5"/>
+      <c r="K38" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O38">
+        <v>15625000</v>
+      </c>
+      <c r="P38" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q38" s="16">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12" t="s">
+        <v>156250000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A39" s="26"/>
+      <c r="B39" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12" t="s">
+      <c r="D39" s="5"/>
+      <c r="E39" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="9" t="s">
         <v>16</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
-      <c r="J39" s="7"/>
-      <c r="K39" s="20">
+      <c r="J39" s="5"/>
+      <c r="K39" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39">
+        <v>10000</v>
+      </c>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12" t="s">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A40" s="26"/>
+      <c r="B40" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C40">
         <v>50000</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="7"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12" t="s">
+      <c r="D40" s="5"/>
+      <c r="E40" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I40">
         <v>50000</v>
       </c>
-      <c r="J40" s="7"/>
-      <c r="K40" s="20">
+      <c r="J40" s="5"/>
+      <c r="K40" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="O40">
+        <v>1250000</v>
+      </c>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="11"/>
-      <c r="B41" s="12" t="s">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A41" s="26"/>
+      <c r="B41" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="20">
+      <c r="D41" s="5"/>
+      <c r="E41" s="16">
         <f>(C41*D41)/24</f>
         <v>0</v>
       </c>
-      <c r="F41" s="7"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12" t="s">
+      <c r="F41" s="5"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I41">
         <v>1</v>
       </c>
-      <c r="J41" s="7"/>
-      <c r="K41" s="20">
+      <c r="J41" s="5"/>
+      <c r="K41" s="16">
         <f>(I41*J41)/24</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12" t="s">
+      <c r="L41" s="5"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="O41">
+        <v>156250000</v>
+      </c>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A42" s="26"/>
+      <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C42">
         <v>10000</v>
       </c>
-      <c r="D42" s="7"/>
-      <c r="E42" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="12" t="s">
+      <c r="D42" s="5"/>
+      <c r="E42" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="5"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I42">
         <v>10000</v>
       </c>
-      <c r="J42" s="7"/>
-      <c r="K42" s="20">
-        <f t="shared" ref="K42:K53" si="8">I42*J42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12" t="s">
+      <c r="J42" s="5"/>
+      <c r="K42" s="16">
+        <f t="shared" ref="K42:K43" si="11">I42*J42</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A43" s="26"/>
+      <c r="B43" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C43">
         <v>40000</v>
       </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="12" t="s">
+      <c r="D43" s="5"/>
+      <c r="E43" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="5"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I43">
         <v>40000</v>
       </c>
-      <c r="J43" s="7"/>
-      <c r="K43" s="20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="17"/>
-      <c r="B44" s="16" t="s">
+      <c r="J43" s="5"/>
+      <c r="K43" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O43">
+        <v>50000</v>
+      </c>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="13"/>
+      <c r="B44" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="22">
+      <c r="C44" s="23"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="18">
         <f>SUM(E31:E43)</f>
         <v>235000</v>
       </c>
-      <c r="F44" s="23"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="16" t="s">
+      <c r="F44" s="19"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="I44" s="16"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="22">
+      <c r="I44" s="23"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="18">
         <f>SUM(K31:K43)</f>
         <v>235000</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
+      <c r="L44" s="19"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="16">
+        <f>(O44*P44)/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A45" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C45">
         <v>37500</v>
       </c>
-      <c r="D45" s="7"/>
-      <c r="E45" s="20">
+      <c r="D45" s="5"/>
+      <c r="E45" s="16">
         <f>D45*C45</f>
         <v>0</v>
       </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="11" t="s">
+      <c r="F45" s="5"/>
+      <c r="G45" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H45" s="12" t="s">
+      <c r="H45" s="9" t="s">
         <v>41</v>
       </c>
       <c r="I45">
         <v>37500</v>
       </c>
-      <c r="J45" s="7"/>
-      <c r="K45" s="20">
+      <c r="J45" s="5"/>
+      <c r="K45" s="16">
         <f>J45*I45</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12" t="s">
+      <c r="L45" s="5"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O45">
+        <v>10000</v>
+      </c>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A46" s="26"/>
+      <c r="B46" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C46">
         <v>500</v>
       </c>
-      <c r="D46" s="13">
-        <v>10</v>
-      </c>
-      <c r="E46" s="20">
-        <f t="shared" ref="E46:E58" si="9">D46*C46</f>
+      <c r="D46" s="10">
+        <v>10</v>
+      </c>
+      <c r="E46" s="16">
+        <f t="shared" ref="E46:E58" si="12">D46*C46</f>
         <v>5000</v>
       </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="12" t="s">
+      <c r="F46" s="5"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="9" t="s">
         <v>42</v>
       </c>
       <c r="I46">
         <v>500</v>
       </c>
-      <c r="J46" s="13">
-        <v>10</v>
-      </c>
-      <c r="K46" s="20">
-        <f t="shared" ref="K46:K58" si="10">J46*I46</f>
+      <c r="J46" s="10">
+        <v>10</v>
+      </c>
+      <c r="K46" s="16">
+        <f t="shared" ref="K46:K55" si="13">J46*I46</f>
         <v>5000</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
-      <c r="B47" s="12" t="s">
+      <c r="L46" s="5"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="O46">
+        <v>40000</v>
+      </c>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A47" s="26"/>
+      <c r="B47" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C47">
         <v>5000</v>
       </c>
-      <c r="D47" s="13">
-        <v>10</v>
-      </c>
-      <c r="E47" s="20">
-        <f t="shared" si="9"/>
+      <c r="D47" s="10">
+        <v>10</v>
+      </c>
+      <c r="E47" s="16">
+        <f t="shared" si="12"/>
         <v>50000</v>
       </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="12" t="s">
+      <c r="F47" s="5"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="9" t="s">
         <v>43</v>
       </c>
       <c r="I47">
         <v>5000</v>
       </c>
-      <c r="J47" s="13">
-        <v>10</v>
-      </c>
-      <c r="K47" s="20">
-        <f t="shared" si="10"/>
+      <c r="J47" s="10">
+        <v>10</v>
+      </c>
+      <c r="K47" s="16">
+        <f t="shared" si="13"/>
         <v>50000</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12" t="s">
+      <c r="L47" s="5"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O47">
+        <v>8</v>
+      </c>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A48" s="26"/>
+      <c r="B48" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C48">
         <v>2000</v>
       </c>
-      <c r="D48" s="13">
-        <v>10</v>
-      </c>
-      <c r="E48" s="20">
-        <f t="shared" si="9"/>
+      <c r="D48" s="10">
+        <v>10</v>
+      </c>
+      <c r="E48" s="16">
+        <f t="shared" si="12"/>
         <v>20000</v>
       </c>
-      <c r="F48" s="7"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="12" t="s">
+      <c r="F48" s="5"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="9" t="s">
         <v>44</v>
       </c>
       <c r="I48">
         <v>2000</v>
       </c>
-      <c r="J48" s="13">
-        <v>10</v>
-      </c>
-      <c r="K48" s="20">
-        <f t="shared" si="10"/>
+      <c r="J48" s="10">
+        <v>10</v>
+      </c>
+      <c r="K48" s="16">
+        <f t="shared" si="13"/>
         <v>20000</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12" t="s">
+      <c r="L48" s="5"/>
+      <c r="N48" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="O48" s="23"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="18">
+        <f>SUM(Q26:Q47)</f>
+        <v>156275000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A49" s="26"/>
+      <c r="B49" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C49">
         <v>20000</v>
       </c>
-      <c r="D49" s="13">
-        <v>10</v>
-      </c>
-      <c r="E49" s="20">
-        <f t="shared" si="9"/>
+      <c r="D49" s="10">
+        <v>10</v>
+      </c>
+      <c r="E49" s="16">
+        <f t="shared" si="12"/>
         <v>200000</v>
       </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="12" t="s">
+      <c r="F49" s="5"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="9" t="s">
         <v>45</v>
       </c>
       <c r="I49">
         <v>20000</v>
       </c>
-      <c r="J49" s="13">
-        <v>10</v>
-      </c>
-      <c r="K49" s="20">
-        <f t="shared" si="10"/>
+      <c r="J49" s="10">
+        <v>10</v>
+      </c>
+      <c r="K49" s="16">
+        <f t="shared" si="13"/>
         <v>200000</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12" t="s">
+      <c r="L49" s="5"/>
+      <c r="M49" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="O49" s="20">
+        <v>60000</v>
+      </c>
+      <c r="P49" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q49" s="16">
+        <f>O49*P49</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A50" s="26"/>
+      <c r="B50" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C50">
         <v>250000</v>
       </c>
-      <c r="D50" s="7"/>
-      <c r="E50" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="7"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="12" t="s">
+      <c r="D50" s="5"/>
+      <c r="E50" s="16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="5"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="9" t="s">
         <v>46</v>
       </c>
       <c r="I50">
         <v>250000</v>
       </c>
-      <c r="J50" s="7"/>
-      <c r="K50" s="20">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12" t="s">
+      <c r="J50" s="5"/>
+      <c r="K50" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="5"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="O50" s="20">
+        <v>60000</v>
+      </c>
+      <c r="P50" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="16">
+        <f t="shared" ref="Q50:Q57" si="14">O50*P50</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A51" s="26"/>
+      <c r="B51" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C51">
         <v>2500000</v>
       </c>
-      <c r="D51" s="7"/>
-      <c r="E51" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="12" t="s">
+      <c r="D51" s="5"/>
+      <c r="E51" s="16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="5"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="9" t="s">
         <v>47</v>
       </c>
       <c r="I51">
         <v>2500000</v>
       </c>
-      <c r="J51" s="7"/>
-      <c r="K51" s="20">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12" t="s">
+      <c r="J51" s="5"/>
+      <c r="K51" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="5"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O51" s="9">
+        <v>5</v>
+      </c>
+      <c r="P51" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q51" s="16">
+        <f t="shared" si="14"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A52" s="26"/>
+      <c r="B52" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C52">
         <v>31250000</v>
       </c>
-      <c r="D52" s="7"/>
-      <c r="E52" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="7"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="12" t="s">
+      <c r="D52" s="5"/>
+      <c r="E52" s="16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="5"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="9" t="s">
         <v>48</v>
       </c>
       <c r="I52">
         <v>31250000</v>
       </c>
-      <c r="J52" s="7"/>
-      <c r="K52" s="20">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="11"/>
-      <c r="B53" s="12" t="s">
+      <c r="J52" s="5"/>
+      <c r="K52" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="5"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O52" s="9">
+        <v>1500</v>
+      </c>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A53" s="26"/>
+      <c r="B53" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C53">
         <v>312500000</v>
       </c>
-      <c r="D53" s="7"/>
-      <c r="E53" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="7"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="12" t="s">
+      <c r="D53" s="5"/>
+      <c r="E53" s="16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="5"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="9" t="s">
         <v>49</v>
       </c>
       <c r="I53">
         <v>312500000</v>
       </c>
-      <c r="J53" s="7"/>
-      <c r="K53" s="20">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12" t="s">
+      <c r="J53" s="5"/>
+      <c r="K53" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="5"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O53" s="9">
+        <v>4000</v>
+      </c>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A54" s="26"/>
+      <c r="B54" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
-      <c r="D54" s="7"/>
-      <c r="E54" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="7"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="12" t="s">
+      <c r="D54" s="5"/>
+      <c r="E54" s="16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="5"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="9" t="s">
         <v>16</v>
       </c>
       <c r="I54">
         <v>1</v>
       </c>
-      <c r="J54" s="7"/>
-      <c r="K54" s="20">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12" t="s">
+      <c r="J54" s="5"/>
+      <c r="K54" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L54" s="5"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O54" s="9">
+        <v>4000</v>
+      </c>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A55" s="26"/>
+      <c r="B55" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C55">
         <v>50000</v>
       </c>
-      <c r="D55" s="7"/>
-      <c r="E55" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="7"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="12" t="s">
+      <c r="D55" s="5"/>
+      <c r="E55" s="16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="5"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I55">
         <v>50000</v>
       </c>
-      <c r="J55" s="7"/>
-      <c r="K55" s="20">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12" t="s">
+      <c r="J55" s="5"/>
+      <c r="K55" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="5"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O55" s="9">
+        <v>25000</v>
+      </c>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A56" s="26"/>
+      <c r="B56" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
-      <c r="D56" s="7"/>
-      <c r="E56" s="20">
+      <c r="D56" s="5"/>
+      <c r="E56" s="16">
         <f>(D56*C56)/24</f>
         <v>0</v>
       </c>
-      <c r="F56" s="7"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="12" t="s">
+      <c r="F56" s="5"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I56">
         <v>1</v>
       </c>
-      <c r="J56" s="7"/>
-      <c r="K56" s="20">
+      <c r="J56" s="5"/>
+      <c r="K56" s="16">
         <f>(J56*I56)/24</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12" t="s">
+      <c r="L56" s="5"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
+      </c>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A57" s="26"/>
+      <c r="B57" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C57">
         <v>10000</v>
       </c>
-      <c r="D57" s="7"/>
-      <c r="E57" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="7"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="12" t="s">
+      <c r="D57" s="5"/>
+      <c r="E57" s="16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="5"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I57">
         <v>10000</v>
       </c>
-      <c r="J57" s="7"/>
-      <c r="K57" s="20">
-        <f t="shared" ref="K57:K69" si="11">J57*I57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="25"/>
-      <c r="B58" s="12" t="s">
+      <c r="J57" s="5"/>
+      <c r="K57" s="16">
+        <f t="shared" ref="K57:K58" si="15">J57*I57</f>
+        <v>0</v>
+      </c>
+      <c r="L57" s="5"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O57">
+        <v>50000</v>
+      </c>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A58" s="8"/>
+      <c r="B58" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C58">
         <v>40000</v>
       </c>
-      <c r="D58" s="7"/>
-      <c r="E58" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="7"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="12" t="s">
+      <c r="D58" s="5"/>
+      <c r="E58" s="16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="5"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I58">
         <v>40000</v>
       </c>
-      <c r="J58" s="7"/>
-      <c r="K58" s="20">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="17"/>
-      <c r="B59" s="16" t="s">
+      <c r="J58" s="5"/>
+      <c r="K58" s="16">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="5"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O58">
+        <v>1</v>
+      </c>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="16">
+        <f>(O58*P58)/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="13"/>
+      <c r="B59" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="16"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="22">
+      <c r="C59" s="23"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="18">
         <f>SUM(E45:E58)</f>
         <v>275000</v>
       </c>
-      <c r="F59" s="23"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="16" t="s">
+      <c r="F59" s="19"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="I59" s="16"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="22">
+      <c r="I59" s="23"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="18">
         <f>SUM(K45:K58)</f>
         <v>275000</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="11" t="s">
+      <c r="L59" s="19"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O59">
+        <v>10000</v>
+      </c>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="16">
+        <f t="shared" ref="Q59:Q61" si="16">O59*P59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A60" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C60">
         <v>37500</v>
       </c>
-      <c r="D60" s="7"/>
-      <c r="E60" s="20">
+      <c r="D60" s="5"/>
+      <c r="E60" s="16">
         <f>D60*C60</f>
         <v>0</v>
       </c>
-      <c r="F60" s="7"/>
-      <c r="G60" s="11" t="s">
+      <c r="F60" s="5"/>
+      <c r="G60" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H60" s="12" t="s">
+      <c r="H60" s="9" t="s">
         <v>41</v>
       </c>
       <c r="I60">
         <v>37500</v>
       </c>
-      <c r="J60" s="7"/>
-      <c r="K60" s="20">
+      <c r="J60" s="5"/>
+      <c r="K60" s="16">
         <f>J60*I60</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12" t="s">
+      <c r="L60" s="5"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="O60">
+        <v>40000</v>
+      </c>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="26"/>
+      <c r="B61" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C61">
         <v>5</v>
       </c>
-      <c r="D61" s="13">
-        <v>10</v>
-      </c>
-      <c r="E61" s="20">
-        <f t="shared" ref="E61:E70" si="12">D61*C61</f>
+      <c r="D61" s="10">
+        <v>10</v>
+      </c>
+      <c r="E61" s="16">
+        <f t="shared" ref="E61:E70" si="17">D61*C61</f>
         <v>50</v>
       </c>
-      <c r="F61" s="7"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="12" t="s">
+      <c r="F61" s="5"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I61">
         <v>5</v>
       </c>
-      <c r="J61" s="13">
-        <v>10</v>
-      </c>
-      <c r="K61" s="20">
-        <f t="shared" ref="K61:K70" si="13">J61*I61</f>
+      <c r="J61" s="10">
+        <v>10</v>
+      </c>
+      <c r="K61" s="16">
+        <f t="shared" ref="K61:K67" si="18">J61*I61</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12" t="s">
+      <c r="L61" s="5"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O61">
+        <v>8</v>
+      </c>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="26"/>
+      <c r="B62" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C62">
         <v>1500</v>
       </c>
-      <c r="D62" s="13">
-        <v>10</v>
-      </c>
-      <c r="E62" s="20">
-        <f t="shared" si="12"/>
+      <c r="D62" s="10">
+        <v>10</v>
+      </c>
+      <c r="E62" s="16">
+        <f t="shared" si="17"/>
         <v>15000</v>
       </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="12" t="s">
+      <c r="F62" s="5"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I62">
         <v>1500</v>
       </c>
-      <c r="J62" s="13">
-        <v>10</v>
-      </c>
-      <c r="K62" s="20">
-        <f t="shared" si="13"/>
+      <c r="J62" s="10">
+        <v>10</v>
+      </c>
+      <c r="K62" s="16">
+        <f t="shared" si="18"/>
         <v>15000</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12" t="s">
+      <c r="L62" s="5"/>
+      <c r="N62" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="O62" s="23"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="21">
+        <f>SUM(Q49:Q61)</f>
+        <v>1200050</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" s="26"/>
+      <c r="B63" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C63">
         <v>4000</v>
       </c>
-      <c r="D63" s="13">
-        <v>10</v>
-      </c>
-      <c r="E63" s="20">
-        <f t="shared" si="12"/>
+      <c r="D63" s="10">
+        <v>10</v>
+      </c>
+      <c r="E63" s="16">
+        <f t="shared" si="17"/>
         <v>40000</v>
       </c>
-      <c r="F63" s="7"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="12" t="s">
+      <c r="F63" s="5"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="9" t="s">
         <v>53</v>
       </c>
       <c r="I63">
         <v>4000</v>
       </c>
-      <c r="J63" s="13">
-        <v>10</v>
-      </c>
-      <c r="K63" s="20">
-        <f t="shared" si="13"/>
+      <c r="J63" s="10">
+        <v>10</v>
+      </c>
+      <c r="K63" s="16">
+        <f t="shared" si="18"/>
         <v>40000</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" s="11"/>
-      <c r="B64" s="12" t="s">
+      <c r="L63" s="5"/>
+      <c r="N63" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="O63" s="24"/>
+      <c r="P63" s="24"/>
+      <c r="Q63" s="16"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" s="26"/>
+      <c r="B64" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C64">
         <v>4000</v>
       </c>
-      <c r="D64" s="13">
-        <v>10</v>
-      </c>
-      <c r="E64" s="20">
-        <f t="shared" si="12"/>
+      <c r="D64" s="10">
+        <v>10</v>
+      </c>
+      <c r="E64" s="16">
+        <f t="shared" si="17"/>
         <v>40000</v>
       </c>
-      <c r="F64" s="7"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="12" t="s">
+      <c r="F64" s="5"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="9" t="s">
         <v>54</v>
       </c>
       <c r="I64">
         <v>4000</v>
       </c>
-      <c r="J64" s="13">
-        <v>10</v>
-      </c>
-      <c r="K64" s="20">
-        <f t="shared" si="13"/>
+      <c r="J64" s="10">
+        <v>10</v>
+      </c>
+      <c r="K64" s="16">
+        <f t="shared" si="18"/>
         <v>40000</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12" t="s">
+      <c r="L64" s="5"/>
+      <c r="N64" s="25"/>
+      <c r="O64" s="25"/>
+      <c r="P64" s="25"/>
+      <c r="Q64" s="11">
+        <f>SUM(Q62+Q48+Q25)</f>
+        <v>50177045050</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A65" s="26"/>
+      <c r="B65" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C65">
         <v>25000</v>
       </c>
-      <c r="D65" s="13">
-        <v>10</v>
-      </c>
-      <c r="E65" s="20">
-        <f t="shared" si="12"/>
+      <c r="D65" s="10">
+        <v>10</v>
+      </c>
+      <c r="E65" s="16">
+        <f t="shared" si="17"/>
         <v>250000</v>
       </c>
-      <c r="F65" s="7"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="12" t="s">
+      <c r="F65" s="5"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="9" t="s">
         <v>55</v>
       </c>
       <c r="I65">
         <v>25000</v>
       </c>
-      <c r="J65" s="13">
-        <v>10</v>
-      </c>
-      <c r="K65" s="20">
-        <f t="shared" si="13"/>
+      <c r="J65" s="10">
+        <v>10</v>
+      </c>
+      <c r="K65" s="16">
+        <f t="shared" si="18"/>
         <v>250000</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12" t="s">
+      <c r="L65" s="5"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A66" s="26"/>
+      <c r="B66" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
-      <c r="D66" s="13">
-        <v>10</v>
-      </c>
-      <c r="E66" s="20">
-        <f t="shared" si="12"/>
-        <v>10</v>
-      </c>
-      <c r="F66" s="7"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="12" t="s">
+      <c r="D66" s="10">
+        <v>10</v>
+      </c>
+      <c r="E66" s="16">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="F66" s="5"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="9" t="s">
         <v>16</v>
       </c>
       <c r="I66">
         <v>1</v>
       </c>
-      <c r="J66" s="13">
-        <v>10</v>
-      </c>
-      <c r="K66" s="20">
-        <f t="shared" si="13"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A67" s="11"/>
-      <c r="B67" s="12" t="s">
+      <c r="J66" s="10">
+        <v>10</v>
+      </c>
+      <c r="K66" s="16">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="L66" s="5"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A67" s="26"/>
+      <c r="B67" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C67">
         <v>50000</v>
       </c>
-      <c r="D67" s="13">
-        <v>10</v>
-      </c>
-      <c r="E67" s="20">
-        <f t="shared" si="12"/>
+      <c r="D67" s="10">
+        <v>10</v>
+      </c>
+      <c r="E67" s="16">
+        <f t="shared" si="17"/>
         <v>500000</v>
       </c>
-      <c r="F67" s="7"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="12" t="s">
+      <c r="F67" s="5"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I67">
         <v>50000</v>
       </c>
-      <c r="J67" s="13">
-        <v>10</v>
-      </c>
-      <c r="K67" s="20">
-        <f t="shared" si="13"/>
+      <c r="J67" s="10">
+        <v>10</v>
+      </c>
+      <c r="K67" s="16">
+        <f t="shared" si="18"/>
         <v>500000</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12" t="s">
+      <c r="L67" s="5"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A68" s="26"/>
+      <c r="B68" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
-      <c r="D68" s="13">
-        <v>10</v>
-      </c>
-      <c r="E68" s="20">
+      <c r="D68" s="10">
+        <v>10</v>
+      </c>
+      <c r="E68" s="16">
         <f>(D68*C68)/24</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="12" t="s">
+      <c r="F68" s="5"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I68">
         <v>1</v>
       </c>
-      <c r="J68" s="13">
-        <v>10</v>
-      </c>
-      <c r="K68" s="20">
+      <c r="J68" s="10">
+        <v>10</v>
+      </c>
+      <c r="K68" s="16">
         <f>(J68*I68)/24</f>
         <v>0.41666666666666669</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12" t="s">
+      <c r="L68" s="5"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A69" s="26"/>
+      <c r="B69" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C69">
         <v>10000</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F69" s="7"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="12" t="s">
+      <c r="D69" s="10"/>
+      <c r="E69" s="16">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I69">
         <v>10000</v>
       </c>
-      <c r="J69" s="7"/>
-      <c r="K69" s="20">
-        <f t="shared" ref="K69:K78" si="14">J69*I69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12" t="s">
+      <c r="J69" s="5"/>
+      <c r="K69" s="16">
+        <f t="shared" ref="K69:K70" si="19">J69*I69</f>
+        <v>0</v>
+      </c>
+      <c r="L69" s="5"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A70" s="26"/>
+      <c r="B70" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C70">
         <v>40000</v>
       </c>
-      <c r="D70" s="13"/>
-      <c r="E70" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F70" s="7"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="12" t="s">
+      <c r="D70" s="10"/>
+      <c r="E70" s="16">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="5"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I70">
         <v>40000</v>
       </c>
-      <c r="J70" s="7"/>
-      <c r="K70" s="20">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B71" s="16" t="s">
+      <c r="J70" s="5"/>
+      <c r="K70" s="16">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L70" s="5"/>
+    </row>
+    <row r="71" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C71" s="16"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="26">
+      <c r="C71" s="23"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="21">
         <f>SUM(E60:E70)</f>
         <v>845060.41666666663</v>
       </c>
-      <c r="F71" s="27"/>
-      <c r="H71" s="16" t="s">
+      <c r="F71" s="22"/>
+      <c r="H71" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="I71" s="16"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="26">
+      <c r="I71" s="23"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="21">
         <f>SUM(K60:K70)</f>
         <v>845060.41666666663</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="11" t="s">
+      <c r="L71" s="22"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A72" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C72">
         <v>12</v>
       </c>
-      <c r="D72" s="7"/>
-      <c r="E72" s="20">
+      <c r="D72" s="5"/>
+      <c r="E72" s="16">
         <f>D72*C72</f>
         <v>0</v>
       </c>
-      <c r="F72" s="7"/>
-      <c r="G72" s="11" t="s">
+      <c r="F72" s="5"/>
+      <c r="G72" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="H72" s="12" t="s">
+      <c r="H72" s="9" t="s">
         <v>57</v>
       </c>
       <c r="I72">
         <v>12</v>
       </c>
-      <c r="J72" s="7"/>
-      <c r="K72" s="20">
+      <c r="J72" s="5"/>
+      <c r="K72" s="16">
         <f>J72*I72</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12" t="s">
+      <c r="L72" s="5"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A73" s="26"/>
+      <c r="B73" s="9" t="s">
         <v>58</v>
       </c>
       <c r="C73">
         <v>12</v>
       </c>
-      <c r="D73" s="7"/>
-      <c r="E73" s="20">
-        <f t="shared" ref="E73:E82" si="15">D73*C73</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="7"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="12" t="s">
+      <c r="D73" s="5"/>
+      <c r="E73" s="16">
+        <f t="shared" ref="E73:E82" si="20">D73*C73</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="9" t="s">
         <v>58</v>
       </c>
       <c r="I73">
         <v>12</v>
       </c>
-      <c r="J73" s="7"/>
-      <c r="K73" s="20">
-        <f t="shared" ref="K73:K82" si="16">J73*I73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12" t="s">
+      <c r="J73" s="5"/>
+      <c r="K73" s="16">
+        <f t="shared" ref="K73:K82" si="21">J73*I73</f>
+        <v>0</v>
+      </c>
+      <c r="L73" s="5"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A74" s="26"/>
+      <c r="B74" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C74">
         <v>37500</v>
       </c>
-      <c r="D74" s="7"/>
-      <c r="E74" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="7"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="12" t="s">
+      <c r="D74" s="5"/>
+      <c r="E74" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="9" t="s">
         <v>41</v>
       </c>
       <c r="I74">
         <v>37500</v>
       </c>
-      <c r="J74" s="7"/>
-      <c r="K74" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12" t="s">
+      <c r="J74" s="5"/>
+      <c r="K74" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L74" s="5"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A75" s="26"/>
+      <c r="B75" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
-      <c r="D75" s="7"/>
-      <c r="E75" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="7"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="12" t="s">
+      <c r="D75" s="5"/>
+      <c r="E75" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I75">
         <v>1</v>
       </c>
-      <c r="J75" s="7"/>
-      <c r="K75" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12" t="s">
+      <c r="J75" s="5"/>
+      <c r="K75" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L75" s="5"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A76" s="26"/>
+      <c r="B76" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C76">
         <v>50000</v>
       </c>
-      <c r="D76" s="7"/>
-      <c r="E76" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="7"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="12" t="s">
+      <c r="D76" s="5"/>
+      <c r="E76" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I76">
         <v>50000</v>
       </c>
-      <c r="J76" s="7"/>
-      <c r="K76" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12" t="s">
+      <c r="J76" s="5"/>
+      <c r="K76" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L76" s="5"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A77" s="26"/>
+      <c r="B77" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
-      <c r="D77" s="7"/>
-      <c r="E77" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F77" s="7"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="12" t="s">
+      <c r="D77" s="5"/>
+      <c r="E77" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="9" t="s">
         <v>16</v>
       </c>
       <c r="I77">
         <v>1</v>
       </c>
-      <c r="J77" s="7"/>
-      <c r="K77" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12" t="s">
+      <c r="J77" s="5"/>
+      <c r="K77" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L77" s="5"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A78" s="26"/>
+      <c r="B78" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C78">
         <v>10000</v>
       </c>
-      <c r="D78" s="7"/>
-      <c r="E78" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F78" s="7"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="12" t="s">
+      <c r="D78" s="5"/>
+      <c r="E78" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F78" s="5"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I78">
         <v>10000</v>
       </c>
-      <c r="J78" s="7"/>
-      <c r="K78" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12" t="s">
+      <c r="J78" s="5"/>
+      <c r="K78" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="5"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A79" s="26"/>
+      <c r="B79" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C79">
         <v>40000</v>
       </c>
-      <c r="D79" s="7"/>
-      <c r="E79" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="7"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="12" t="s">
+      <c r="D79" s="5"/>
+      <c r="E79" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="5"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I79">
         <v>40000</v>
       </c>
-      <c r="J79" s="7"/>
-      <c r="K79" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12" t="s">
+      <c r="J79" s="5"/>
+      <c r="K79" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L79" s="5"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A80" s="26"/>
+      <c r="B80" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C80">
         <v>8</v>
       </c>
-      <c r="D80" s="7"/>
-      <c r="E80" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="7"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="12" t="s">
+      <c r="D80" s="5"/>
+      <c r="E80" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="5"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="9" t="s">
         <v>59</v>
       </c>
       <c r="I80">
         <v>8</v>
       </c>
-      <c r="J80" s="7"/>
-      <c r="K80" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A81" s="11"/>
-      <c r="B81" s="12" t="s">
+      <c r="J80" s="5"/>
+      <c r="K80" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L80" s="5"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81" s="26"/>
+      <c r="B81" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C81">
         <v>500</v>
       </c>
-      <c r="D81" s="7"/>
-      <c r="E81" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F81" s="7"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="12" t="s">
+      <c r="D81" s="5"/>
+      <c r="E81" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="5"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="9" t="s">
         <v>60</v>
       </c>
       <c r="I81">
         <v>500</v>
       </c>
-      <c r="J81" s="7"/>
-      <c r="K81" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="11"/>
-      <c r="B82" s="12" t="s">
+      <c r="J81" s="5"/>
+      <c r="K81" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L81" s="5"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A82" s="26"/>
+      <c r="B82" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C82">
         <v>60000</v>
       </c>
-      <c r="D82" s="7"/>
-      <c r="E82" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F82" s="7"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="12" t="s">
+      <c r="D82" s="5"/>
+      <c r="E82" s="16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="5"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="9" t="s">
         <v>61</v>
       </c>
       <c r="I82">
         <v>60000</v>
       </c>
-      <c r="J82" s="7"/>
-      <c r="K82" s="20">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B83" s="16" t="s">
+      <c r="J82" s="5"/>
+      <c r="K82" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L82" s="5"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B83" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C83" s="16"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="20">
+      <c r="C83" s="23"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="16">
         <f>SUM(E72:E82)</f>
         <v>0</v>
       </c>
-      <c r="F83" s="7"/>
-      <c r="H83" s="16" t="s">
+      <c r="F83" s="5"/>
+      <c r="H83" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="I83" s="16"/>
-      <c r="J83" s="7"/>
-      <c r="K83" s="20">
+      <c r="I83" s="23"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="16">
         <f>SUM(K72:K82)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B84" s="28" t="s">
+      <c r="L83" s="5"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B84" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="7"/>
-      <c r="H84" s="28" t="s">
+      <c r="C84" s="24"/>
+      <c r="D84" s="24"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="5"/>
+      <c r="H84" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I84" s="28"/>
-      <c r="J84" s="28"/>
-      <c r="K84" s="20"/>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B85" s="29"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="14">
+      <c r="I84" s="24"/>
+      <c r="J84" s="24"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="5"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B85" s="25"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="11">
         <f>SUM(E83+E71+E59+E44+E30+E17)</f>
         <v>31901727.083333336</v>
       </c>
-      <c r="F85" s="13"/>
-      <c r="H85" s="29"/>
-      <c r="I85" s="29"/>
-      <c r="J85" s="29"/>
-      <c r="K85" s="14">
+      <c r="F85" s="10"/>
+      <c r="H85" s="25"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="11">
         <f>SUM(K83+K71+K59+K44+K30+K17)</f>
         <v>31901727.083333336</v>
       </c>
+      <c r="L85" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="37">
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="N63:P64"/>
+    <mergeCell ref="M26:M46"/>
+    <mergeCell ref="M49:M61"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="M4:M24"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A4:A16"/>
+    <mergeCell ref="G4:G16"/>
+    <mergeCell ref="A18:A29"/>
+    <mergeCell ref="G18:G29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A31:A43"/>
+    <mergeCell ref="G31:G43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A45:A57"/>
+    <mergeCell ref="G45:G57"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="H59:I59"/>
     <mergeCell ref="B83:C83"/>
     <mergeCell ref="H83:I83"/>
     <mergeCell ref="B84:D85"/>
@@ -3139,26 +4044,10 @@
     <mergeCell ref="H71:I71"/>
     <mergeCell ref="A72:A82"/>
     <mergeCell ref="G72:G82"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A45:A57"/>
-    <mergeCell ref="G45:G57"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="A18:A29"/>
-    <mergeCell ref="G18:G29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A31:A43"/>
-    <mergeCell ref="G31:G43"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A4:A16"/>
-    <mergeCell ref="G4:G16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="H17:I17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="Q21" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>